--- a/光伏配储项目/电价数据/2026/嘉应站.xlsx
+++ b/光伏配储项目/电价数据/2026/嘉应站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.4365</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.78304</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.48462</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.50537</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.44201</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44619</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.40889</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.38634</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.42644</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.2409</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.14317</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.00371</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.08452</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.08827</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.07391</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5112599999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5559299999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.74075</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14255</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.35212</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43347</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44021</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66652</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.88825</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.21379</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.34554</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.1799</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.02689</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.30724</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.40803</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45336</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7042200000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.75561</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.11632</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.9498799999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.9084099999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.80636</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.76844</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51846</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4892</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46918</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42048</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43072</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7298600000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.90573</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.96851</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51166</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5389400000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.51885</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5189900000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5004</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40695</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48106</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.49655</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.46497</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.42335</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.42207</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.49627</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.51034</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.40299</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.39654</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.5380499999999999</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.55123</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49685</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.26514</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.02703</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.03302</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>-0.01796</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.10916</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.45762</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.43588</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.59604</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.19622</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.04768</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.04564</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>-0.03487</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.02091</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60134</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.76512</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7925800000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.18556</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.38296</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.13912</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8586900000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.22616</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.12355</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.16342</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.92031</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.1078</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.66706</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.00111</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.92633</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.97765</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.81075</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>-0.03213000000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45444</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>-0.03787</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45414</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43234</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44817</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33538</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5208700000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49997</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49879</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43743</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45442</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40318</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.37583</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40586</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48551</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4473</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22148</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.03912</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>-0.04301</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>-0.02932</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.79595</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.05634</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.4434</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.4328</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.45913</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.31963</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62801</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.66551</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46944</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50718</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43548</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5037699999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.62822</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.44913</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>-0.01361</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>-0.0267</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43641</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46162</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34292</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52279</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.51024</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44452</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39697</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45863</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39401</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42203</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43631</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.03183</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.03909000000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.04281</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.59108</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28158</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21185</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.18404</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.27407</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40665</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.64097</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41152</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.44141</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.02538</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.47388</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.52589</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45115</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47408</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.00048</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.37357</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.49568</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.52128</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.49324</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5046700000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.44594</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.42358</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33035</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.04804</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.26993</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.26166</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.08084999999999999</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04019</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13223</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03977</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03703</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.0669</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.06853000000000001</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.20951</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.23432</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.21627</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.22166</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.26843</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.25859</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.26826</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.24967</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.23702</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.06309000000000001</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.26596</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.11883</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.2562</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.21669</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N122" t="n">
+        <v>-0.00525</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.24601</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.25165</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.23383</v>
+      </c>
+      <c r="S122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="U122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.20759</v>
+      </c>
+      <c r="X122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.23413</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.03608</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.08173</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.25083</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.15091</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10148</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00598</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19851</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04543</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26406</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.14077</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.01016</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05266</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05084</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.28007</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.27531</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.26906</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.23507</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33547</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.2581</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.27278</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43074</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46069</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7857499999999999</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88747</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86975</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6145700000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5565399999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.27164</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.27611</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.27326</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.26771</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.10666</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4269</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.24102</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.27705</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.13555</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.1408</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.05404</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.43857</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8917200000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47673</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>-0.01626</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.10445</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.2051</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>-0.02517</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.80284</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.28732</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.03001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.2591</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.18383</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.60187</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.20974</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.21389</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.27814</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.26849</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.24976</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.28926</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.14892</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.13592</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.16867</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.11438</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.17736</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.25314</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.17581</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.23908</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.23697</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.22926</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.19016</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.19254</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.04603</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.04067</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>-0.03261</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.03588</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.08824</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.25229</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.8140599999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.18228</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.12215</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.08529</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.15434</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-0.00328</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.14851</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.08342000000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.21641</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.19501</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.22163</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.1673</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.23048</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.18329</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.19568</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.23271</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.04043</v>
+      </c>
+      <c r="U125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.17904</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.08084000000000001</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.18741</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.15905</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.12267</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.16316</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.18433</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.21264</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.24019</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.20868</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.23284</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.22777</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.20649</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.27604</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.28137</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.09487000000000001</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.04865</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.27065</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.25981</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.25947</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20422</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.22598</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.25112</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.24611</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.25394</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.22689</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.21402</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26412</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.19691</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.21209</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.23786</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.23485</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.16495</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.2376</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.2026</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.21806</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.19709</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.24627</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.16247</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.23705</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>-0.02387</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.26208</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.24708</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.43635</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.27183</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.20227</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.14397</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.09636</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.70001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.40586</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.12572</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.63179</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7256900000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.5815900000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.15529</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.15934</v>
+      </c>
+      <c r="R126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.03166</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="X126" t="n">
+        <v>-0.03642</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>-0.04075</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>-0.0381</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.01613</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.4045899999999999</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.20661</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.06558</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.16524</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.23585</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.21548</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.26402</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.23969</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.24508</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.11944</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25555</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.26038</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.12233</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.22847</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27751</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26938</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26575</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.26539</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.26581</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.27893</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.25053</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.23611</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.24763</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.20544</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.20662</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.17032</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.16418</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.27103</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.24899</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.09852</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.22113</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.26932</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.25509</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.14186</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.02341</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>-0.00761</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>-0.01696</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.1536</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.16618</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.15872</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.16524</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.19698</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.10457</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.19872</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.09365999999999999</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.05688</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.02805</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.23359</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.04951</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.07908</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.07476999999999999</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.22414</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.22014</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.21978</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.23526</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.2155</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.07232999999999999</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.24338</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>-0.02686</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.12918</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.21938</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.00274</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28687</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.02499</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.005719999999999999</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27208</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.19949</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.02178</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25793</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.23847</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.04703</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.04881</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.19909</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.11353</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.18769</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.12635</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.16241</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.11226</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.04542</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.19403</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.12189</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.19719</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.08581</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.13067</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.08261</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.04667</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.08041</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.06566</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>-0.04515</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>-0.03382</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>-0.03868</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.29345</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.10663</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.11323</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.01588</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.12122</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.17175</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.03447</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.12871</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.11692</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.09878000000000001</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.27801</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.26863</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.1383</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.17388</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.10804</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.14641</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.16676</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.17273</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.1669</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.17757</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.18493</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.17801</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.18493</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.18195</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.15675</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.2081</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.17324</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.20829</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.21534</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.20641</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.21036</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.24519</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.22585</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.25802</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.23497</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.25843</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.18215</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.14253</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.21751</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.17816</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.00967</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.21685</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.26971</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24215</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.20001</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.13308</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.14972</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.17199</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.21656</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.17233</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.22818</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.23566</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.17987</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.25205</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.25789</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.26174</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.25446</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.22178</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.21522</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.24884</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.0501</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.24314</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.23498</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.19115</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.18959</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.14708</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.25496</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.24525</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.21838</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.19859</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.22799</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.06728000000000001</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.13972</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.13266</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.19657</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.17369</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.27059</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.16966</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.14644</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.18778</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.09072</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.13261</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.13112</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.17385</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.16462</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.18247</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.17962</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.24545</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.16206</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.18166</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.18374</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.24168</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.23714</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.18627</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.23844</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.23378</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.18371</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.18386</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.16637</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.07212</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.27855</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.13809</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.16659</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.23882</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.18737</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.17932</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.27049</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.03997</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.58545</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28133</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.27391</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26456</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.26936</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.42619</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.26787</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27155</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.14909</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.24974</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.5156499999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.27011</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.24727</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.40426</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.21857</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.13292</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.22629</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.26789</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.24884</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.24148</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.26695</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.51261</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6169199999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.26963</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.14993</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.21131</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.22044</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.2013</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.10989</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.12363</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.10976</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.12832</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.14469</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.11531</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.06203</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.13044</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.12037</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.14059</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.13904</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.14175</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.14769</v>
+      </c>
+      <c r="R130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.22353</v>
+      </c>
+      <c r="T130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.03096</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.21871</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.22189</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.10869</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.01221</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.16688</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.28026</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.23496</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.24691</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.10338</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.24663</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.26933</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.24699</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.19395</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.15133</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.17301</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.1753</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.21407</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.18437</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.18057</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.18429</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.23209</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.19417</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.22244</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.22542</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.23063</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.18268</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.1727</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.17665</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.13944</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.17506</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.18954</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.16022</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.24795</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.22471</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.04854</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.1458</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.18445</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.19756</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.25389</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.22571</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.19207</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.17672</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.15441</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>-0.04761</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.24386</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.07925</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.26537</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.25728</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.05368</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.25847</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.08093</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.25873</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.05321</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.26934</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.25331</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.02915</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.26616</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.24701</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>-0.04644</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.24661</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.1774</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.24728</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.24628</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.24731</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.24824</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.24773</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.24693</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.11283</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.24627</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.24313</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.24391</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.1436</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.11879</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.23646</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.23693</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.15357</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.07267</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.22127</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.14773</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.23647</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.12266</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.15978</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.11027</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.24193</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.15775</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.14374</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.14203</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.23321</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.13442</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.14162</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.12635</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.13285</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.15764</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.17692</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.2056</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.22894</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.25112</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.25854</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.27341</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.27689</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.29144</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.25098</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.25389</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.19065</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.28356</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.26291</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.25673</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.21159</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.27714</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.26054</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.22804</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.23382</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.23392</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.24859</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.25652</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.26696</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.24684</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.2111</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.20923</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.25566</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.26096</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.2456</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.12551</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.16845</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.17789</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.08875</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.17828</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.27269</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.55184</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.06344</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.008279999999999999</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.05903</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.24725</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.25329</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.25602</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.23644</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.17994</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.27331</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.20563</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.25908</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.25622</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.25588</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.25905</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.25513</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.20516</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.25601</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.24987</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.25702</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.19508</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.25315</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.24911</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.19416</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.25651</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.25684</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.24458</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.07231</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.25581</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.25354</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.2571</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.2571</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.13717</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.26291</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.27691</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.2536</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.25351</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.24822</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.2489</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.25494</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.24164</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.25457</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.28251</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.22806</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.13829</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25031</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.03351</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28379</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.03638</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>-0.00134</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.27808</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.20355</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.04732</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.1508</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.21314</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.27124</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24962</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.27879</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.22659</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26192</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.24578</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.21739</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.22248</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.22579</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.22575</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.16367</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.25597</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.27007</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.11739</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>-0.03357</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.09293999999999999</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.5721900000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5299299999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.56188</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.73582</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.41657</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.02436</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.04593</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.07171999999999999</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.1809</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.27382</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.19588</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.2047</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.08918999999999999</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.08311</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.12166</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.09126999999999999</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.11342</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.08714</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.13457</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.15031</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.15109</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.16803</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.05088</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.12133</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.05363</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.11549</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.01746</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.07195</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.06698</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.04363</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>-0.02157</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>-0.01449</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.29095</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.45566</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.16574</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.25141</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.06177000000000001</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.15134</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.27271</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.26948</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.4070299999999999</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6582</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.7229500000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-0.00015</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.23713</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.27309</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.06568</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.18866</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.24728</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.24576</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.20535</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.2596</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.05742</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>-0.01528</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.66675</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5208400000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.57117</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.09456999999999999</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.06595000000000001</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.03202</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-0.01118</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.00445</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.10666</v>
+      </c>
+      <c r="L134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.02179</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.01893</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.1124</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.12125</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.16049</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.14133</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.25899</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.25578</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.26476</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.04706</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.10109</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.25865</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.26476</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.01116</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.02615</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.27831</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.11223</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.26018</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.25395</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.27198</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.14837</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.28552</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.21754</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.26098</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.14889</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.02606</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.11845</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41347</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.23659</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.04654</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.04212</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.1237</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.22918</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.16943</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.20783</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.1911</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.15367</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.18925</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.13976</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.04568999999999999</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.15802</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>-0.03481</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.0712</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>-0.01005</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.25908</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.09658</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.26054</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.02565</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.11975</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.03308</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.25026</v>
+      </c>
+      <c r="R135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.21144</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>-0.01633</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.00571</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.16387</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.27678</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25478</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.02924</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27422</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.25428</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.24161</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.16108</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.17325</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.17401</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.16092</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.19026</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.25251</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.13822</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>-0.02689</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.06354</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.0563</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.0687</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.12979</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.21407</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>-0.02378</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.08993000000000001</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.01102</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.04149</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>-0.00475</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.07042</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.04222</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>-0.01182</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.03445</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.10913</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>-0.04412</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.006889999999999999</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.07026</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.13511</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.12792</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.13488</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.11396</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.14638</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.00889</v>
+      </c>
+      <c r="O136" t="n">
+        <v>-0.01256</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.2349</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.17461</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00086</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15613</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01428</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04307</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04102</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04829</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02946</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03838</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03561</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01147</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03528</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20797</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27022</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28187</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.20842</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.23808</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.2219</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.25381</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.24641</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.20392</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.19075</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.23421</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.17852</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.14327</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.24983</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24707</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.19177</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.17156</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.17211</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.00063</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.22109</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.15396</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.20957</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.19492</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.18354</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.15845</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.20687</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.23522</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.07443999999999999</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.02812</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-0.0331</v>
+      </c>
+      <c r="I137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.03228</v>
+      </c>
+      <c r="K137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24945</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.07926999999999999</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.2546</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.7905</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8714299999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.28484</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03986</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.16833</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04852</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.00218</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.04469</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29839</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04567</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25442</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.26634</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.17895</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.22615</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.20756</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.21319</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.16024</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.8786499999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.00612</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.74098</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7392300000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.7433500000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.83975</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.23724</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.21103</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.27736</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.14168</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.14152</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I138" t="n">
+        <v>-0.04147</v>
+      </c>
+      <c r="J138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.28623</v>
+      </c>
+      <c r="L138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.03888</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.01111</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.22653</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.04053</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.11418</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.07637000000000001</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.07856999999999999</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.22627</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.12544</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.11095</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.25337</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.28436</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.25575</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.27343</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.26747</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.27757</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.26488</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.26321</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.24136</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.26405</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.24501</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.21628</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.23327</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.19131</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.03679</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>-0.01386</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>-0.01247</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.06420000000000001</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.17036</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.12778</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.13645</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.10655</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.12245</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.16615</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.12207</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.15422</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.11144</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.14831</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.15034</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.16183</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.19904</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.16955</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.16975</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.16961</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.19091</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.19928</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.16917</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.17692</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.17834</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.16483</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.17477</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.17969</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.17976</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.17163</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.17828</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.16835</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.17165</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.16907</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.19438</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.18831</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.13271</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.15216</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>-0.03478</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.16769</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.22093</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.27251</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.28061</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.26302</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.23415</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.2606</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.28202</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.27677</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.27225</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.24918</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.27018</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.28981</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40462</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.7229099999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.50946</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.21229</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.01855</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.44961</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.00508</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.83086</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.02712</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>-0.04649</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.14401</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.27729</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.26099</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.02889</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.14745</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.21822</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.15624</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.19641</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.07687000000000001</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.18581</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.17503</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.18594</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.2465</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.20063</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.1795</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.13514</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.14492</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.16165</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.20367</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.16032</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.27397</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.17594</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.17483</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.16777</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.19543</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.20809</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.20218</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.20359</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.20303</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.17923</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.23575</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.17398</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.17079</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.15853</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.12414</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.13826</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.07704000000000001</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.1224</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.26515</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.21079</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.25822</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.21122</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.27334</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43417</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.27253</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.26539</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.24922</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.24763</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.25341</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.23267</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.26493</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.26976</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.27499</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.4546</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.19037</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.70375</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.51864</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.01703</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.13367</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.27285</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.08245000000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.2556</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.13827</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.04479</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.81702</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7288300000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.48868</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.21616</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.18715</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.21302</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.21901</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.20216</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.19408</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.22469</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.23274</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.27096</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.17142</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.26104</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.25103</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.12863</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.13983</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.13538</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.17821</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.25422</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.17157</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.08187</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.25417</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.24317</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.16125</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.17459</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.15289</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.14801</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.12263</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.2449</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.25861</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.09468</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.07778</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.28657</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.28796</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.26575</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.17406</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.17527</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.21735</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.10185</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.26751</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.22369</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.23031</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27393</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.24827</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.21142</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.20365</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.25323</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.03191</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.18181</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27804</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.03417</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01939</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.18735</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.2005</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03764</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.06174</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.27879</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.23879</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.25504</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.26781</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.26354</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.19876</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.15107</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.21975</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.23354</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26884</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.28009</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.42795</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.1802</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.24722</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.20394</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.20671</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.26212</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43798</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.24025</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.24696</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.16059</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.24251</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.24677</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.16198</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.17679</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.18379</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.22998</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.21546</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.19298</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.22307</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.24341</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.16623</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.24972</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.18237</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.23192</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.24398</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.26774</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.25229</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.25048</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.24903</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.24958</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.25266</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.23496</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.2469</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.24634</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.25725</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.24297</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.22074</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.24857</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.24189</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.26767</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.26127</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.23768</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.23857</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.24441</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.25804</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.26946</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27804</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27273</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.26994</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.28589</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.24103</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.12417</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.28518</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42893</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.27856</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43747</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42106</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.27245</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.26686</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.2599</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.2654</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.17541</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.28554</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.27406</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.23646</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.28154</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42416</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.28152</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.26985</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.26201</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.25419</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.26036</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.26272</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.25828</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.23605</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.07604000000000001</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.24262</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.23744</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.24169</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.24346</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.24347</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.25847</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.28612</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.17825</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.21493</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.22677</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.23222</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.23474</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.25654</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.24742</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.24844</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.22954</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.2428</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.25525</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.24734</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.27468</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17675</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.28903</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14638</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19957</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23735</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04775</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04786</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13464</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.00067</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03522</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17799</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22777</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27099</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15803</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24144</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.22172</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.00384</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20215</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15172</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26448</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27742</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.47949</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.22316</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.27881</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.22594</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.41833</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.27232</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.30789</v>
       </c>
     </row>
   </sheetData>
